--- a/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
+++ b/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>Bill of Material (BOM) for Stadium_Board</t>
   </si>
@@ -48,9 +48,6 @@
     <t>DF06S</t>
   </si>
   <si>
-    <t>0805W8F1002T5E</t>
-  </si>
-  <si>
     <t>U1, U2</t>
   </si>
   <si>
@@ -174,35 +171,42 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>Alibaba</t>
-  </si>
-  <si>
     <t>MagicHome with ESP8285</t>
   </si>
   <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
     <t>CC0603KRX5R8BB475</t>
   </si>
   <si>
     <t>ESR25JZPF5600</t>
   </si>
   <si>
-    <t>RS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quantity </t>
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate part use </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HoAR0805-1/8W-10KR-0.1%-TCR25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do Not Mount </t>
+  </si>
+  <si>
+    <t>Out of Stock on LCSC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,13 +219,14 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,6 +253,13 @@
     <font>
       <strike/>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -280,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -292,7 +304,7 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -308,36 +320,10 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -349,8 +335,8 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -364,51 +350,12 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -430,8 +377,101 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color auto="1"/>
@@ -448,174 +488,153 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -899,481 +918,512 @@
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" thickBot="1">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A3" s="39">
+        <v>1</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="13">
+        <v>3</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A4" s="39">
+        <v>2</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="44"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A5" s="39">
+        <v>3</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="45"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A6" s="39">
+        <v>4</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="44"/>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A7" s="39">
+        <v>5</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="11">
+        <v>4</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="44"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A8" s="39">
+        <v>6</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="16">
+        <v>1</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A9" s="39">
+        <v>7</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="19">
+        <v>2</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A10" s="39">
+        <v>8</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="19">
+        <v>2</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A11" s="39">
+        <v>9</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="37">
+        <v>2</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="38"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A12" s="39">
+        <v>10</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="37">
+        <v>2</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A13" s="39">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A14" s="39">
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A15" s="39">
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="44"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A16" s="39">
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A17" s="39">
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="47"/>
+    </row>
+    <row r="18" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A18" s="39">
+        <v>16</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D18" s="16">
+        <v>2</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="9" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="39">
+        <v>17</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="22">
+        <v>2</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A20" s="39">
+        <v>18</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A21" s="39">
+        <v>19</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="45"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A22" s="39">
+        <v>20</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A23" s="39">
+        <v>21</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="22">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="48"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A24" s="39">
+        <v>22</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="44"/>
+    </row>
+    <row r="25" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A25" s="39">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="26.25" thickBot="1">
+      <c r="A26" s="39">
+        <v>24</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="33">
+        <v>8</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="41" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="14">
-        <v>3</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="10" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="12">
-        <v>4</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="17">
-        <v>1</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="20">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="23">
-        <v>2</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="25">
-        <v>2</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="30">
-        <v>2</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="14">
-        <v>2</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" thickBot="1">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="8" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="17">
-        <v>2</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="10" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="27">
-        <v>2</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="32">
-        <v>1</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="10" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="34">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="55" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11"/>
-    </row>
-    <row r="26" spans="1:6" ht="26.25" thickBot="1">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="49">
-        <v>8</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:D26">
     <cfRule type="colorScale" priority="10">
@@ -1404,25 +1454,20 @@
     <hyperlink ref="E4" r:id="rId2"/>
     <hyperlink ref="E5" r:id="rId3"/>
     <hyperlink ref="E7" r:id="rId4"/>
-    <hyperlink ref="E8" r:id="rId5"/>
-    <hyperlink ref="E9" r:id="rId6"/>
-    <hyperlink ref="E10" r:id="rId7"/>
-    <hyperlink ref="E13" r:id="rId8"/>
-    <hyperlink ref="E14" r:id="rId9"/>
-    <hyperlink ref="E15" r:id="rId10"/>
-    <hyperlink ref="E18" r:id="rId11"/>
-    <hyperlink ref="E20" r:id="rId12"/>
-    <hyperlink ref="E21" r:id="rId13"/>
-    <hyperlink ref="E23" r:id="rId14"/>
-    <hyperlink ref="E22" r:id="rId15"/>
-    <hyperlink ref="E6" r:id="rId16"/>
-    <hyperlink ref="E16" r:id="rId17"/>
-    <hyperlink ref="E17" r:id="rId18"/>
-    <hyperlink ref="E12" r:id="rId19"/>
-    <hyperlink ref="E19" r:id="rId20"/>
-    <hyperlink ref="E24" r:id="rId21"/>
+    <hyperlink ref="E10" r:id="rId5"/>
+    <hyperlink ref="E13" r:id="rId6"/>
+    <hyperlink ref="E14" r:id="rId7"/>
+    <hyperlink ref="E15" r:id="rId8"/>
+    <hyperlink ref="E21" r:id="rId9"/>
+    <hyperlink ref="E23" r:id="rId10"/>
+    <hyperlink ref="E6" r:id="rId11"/>
+    <hyperlink ref="E16" r:id="rId12"/>
+    <hyperlink ref="E17" r:id="rId13"/>
+    <hyperlink ref="E19" r:id="rId14"/>
+    <hyperlink ref="E24" r:id="rId15"/>
+    <hyperlink ref="E18" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
+++ b/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\SH-CircuitCorrections\Deliverables\Stadium_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\SH-CircuitCorrections\Deliverables\Stadium_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389A0D35-7CDD-48D6-AF28-5E3BD9004259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>Bill of Material (BOM) for Stadium_Board</t>
   </si>
@@ -57,9 +58,6 @@
     <t>J1</t>
   </si>
   <si>
-    <t>DC-005-25A</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
@@ -192,20 +190,31 @@
     <t xml:space="preserve">Alternate part use </t>
   </si>
   <si>
-    <t xml:space="preserve">HoAR0805-1/8W-10KR-0.1%-TCR25
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Do Not Mount </t>
   </si>
   <si>
     <t>Out of Stock on LCSC</t>
+  </si>
+  <si>
+    <t>TTI Europe</t>
+  </si>
+  <si>
+    <t>Heisener</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>DC-C024E-7A-1.65</t>
+  </si>
+  <si>
+    <t>0805W8F1002T5E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -488,7 +497,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -552,9 +561,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -591,50 +597,56 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -911,7 +923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -919,19 +931,19 @@
     <col min="2" max="2" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6" ht="16.5" thickBot="1">
       <c r="A2" s="2" t="s">
@@ -944,111 +956,113 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A3" s="39">
+      <c r="A3" s="36">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="13">
         <v>3</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A4" s="39">
-        <v>2</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="36">
+        <v>2</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="41"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A5" s="36">
+        <v>3</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="44"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A5" s="39">
-        <v>3</v>
-      </c>
-      <c r="B5" s="26" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="42"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A6" s="36">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="45"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A6" s="39">
-        <v>4</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="C6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
+      <c r="A7" s="36">
+        <v>5</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="44"/>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A7" s="39">
-        <v>5</v>
-      </c>
-      <c r="B7" s="27" t="s">
+      <c r="C7" s="23" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="11">
         <v>4</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="44"/>
+        <v>48</v>
+      </c>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A8" s="39">
+      <c r="A8" s="36">
         <v>6</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>26</v>
+      <c r="B8" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>4</v>
@@ -1056,34 +1070,38 @@
       <c r="D8" s="16">
         <v>1</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="41" t="s">
+      <c r="E8" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A9" s="36">
+        <v>7</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="19">
+        <v>2</v>
+      </c>
+      <c r="E9" s="48" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A9" s="39">
-        <v>7</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="19">
-        <v>2</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="38" t="s">
-        <v>59</v>
+      <c r="F9" s="35" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A10" s="39">
+      <c r="A10" s="36">
         <v>8</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -1093,200 +1111,202 @@
         <v>2</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="46"/>
+        <v>48</v>
+      </c>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A11" s="39">
+      <c r="A11" s="36">
         <v>9</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="34">
+        <v>2</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="35"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A12" s="36">
+        <v>10</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="34">
+        <v>2</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A13" s="36">
+        <v>11</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="37">
-        <v>2</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="38"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A12" s="39">
-        <v>10</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="37">
-        <v>2</v>
-      </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A13" s="39">
-        <v>11</v>
-      </c>
-      <c r="B13" s="25" t="s">
+      <c r="C13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="D13" s="13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="40"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A14" s="36">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="13">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="43"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A14" s="39">
-        <v>12</v>
-      </c>
-      <c r="B14" s="26" t="s">
+      <c r="C14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="44"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A15" s="36">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="3">
-        <v>2</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="47"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A15" s="39">
-        <v>13</v>
-      </c>
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="41"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A16" s="36">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="3">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="44"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A16" s="39">
-        <v>14</v>
-      </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A17" s="36">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A17" s="39">
-        <v>15</v>
-      </c>
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A18" s="36">
+        <v>16</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="47"/>
-    </row>
-    <row r="18" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A18" s="39">
-        <v>16</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="C18" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="16">
+        <v>2</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="9" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="36">
+        <v>17</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="D19" s="21">
+        <v>2</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="40"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A20" s="36">
+        <v>18</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="16">
-        <v>2</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="9" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="39">
-        <v>17</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="22">
-        <v>2</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="43"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A20" s="39">
-        <v>18</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A21" s="36">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A21" s="39">
-        <v>19</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>10</v>
@@ -1295,100 +1315,102 @@
         <v>2</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="42"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A22" s="36">
+        <v>20</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>49</v>
-      </c>
-      <c r="F21" s="45"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A22" s="39">
-        <v>20</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>50</v>
       </c>
       <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="42" t="s">
-        <v>59</v>
+      <c r="E22" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A23" s="39">
+      <c r="A23" s="36">
         <v>21</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="21">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A24" s="36">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="22">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="48"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A24" s="39">
-        <v>22</v>
-      </c>
-      <c r="B24" s="26" t="s">
+      <c r="C24" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="44"/>
+        <v>48</v>
+      </c>
+      <c r="F24" s="41"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A25" s="39">
+      <c r="A25" s="36">
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
       </c>
       <c r="E25" s="10"/>
-      <c r="F25" s="42" t="s">
-        <v>59</v>
+      <c r="F25" s="39" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="26.25" thickBot="1">
-      <c r="A26" s="39">
+      <c r="A26" s="36">
         <v>24</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="D26" s="32">
+        <v>8</v>
+      </c>
+      <c r="E26" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="33">
-        <v>8</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>58</v>
+      <c r="F26" s="38" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1450,24 +1472,26 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
-    <hyperlink ref="E4" r:id="rId2"/>
-    <hyperlink ref="E5" r:id="rId3"/>
-    <hyperlink ref="E7" r:id="rId4"/>
-    <hyperlink ref="E10" r:id="rId5"/>
-    <hyperlink ref="E13" r:id="rId6"/>
-    <hyperlink ref="E14" r:id="rId7"/>
-    <hyperlink ref="E15" r:id="rId8"/>
-    <hyperlink ref="E21" r:id="rId9"/>
-    <hyperlink ref="E23" r:id="rId10"/>
-    <hyperlink ref="E6" r:id="rId11"/>
-    <hyperlink ref="E16" r:id="rId12"/>
-    <hyperlink ref="E17" r:id="rId13"/>
-    <hyperlink ref="E19" r:id="rId14"/>
-    <hyperlink ref="E24" r:id="rId15"/>
-    <hyperlink ref="E18" r:id="rId16"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E8" r:id="rId16" xr:uid="{8537F03E-8899-43DA-B4A7-2B8A117DE469}"/>
+    <hyperlink ref="E9" r:id="rId17" xr:uid="{27AA9B92-09C1-4A5A-9BE5-16F692BB6C8C}"/>
+    <hyperlink ref="E22" r:id="rId18" xr:uid="{BF70A448-2700-48CC-9B35-ACBBDEFEA5A2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
+++ b/Deliverables/Stadium_Board/BOM/Manufacturer-BOM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\SH-CircuitCorrections\Deliverables\Stadium_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\SH-CircuitCorrections\Deliverables\Stadium_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389A0D35-7CDD-48D6-AF28-5E3BD9004259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
-  <si>
-    <t>Bill of Material (BOM) for Stadium_Board</t>
-  </si>
-  <si>
-    <t>S. No.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="83">
   <si>
     <t>Designator</t>
   </si>
@@ -166,18 +159,9 @@
     <t>------</t>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
     <t>MagicHome with ESP8285</t>
   </si>
   <si>
-    <t>CC0603KRX5R8BB475</t>
-  </si>
-  <si>
-    <t>ESR25JZPF5600</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quantity </t>
   </si>
   <si>
@@ -196,25 +180,101 @@
     <t>Out of Stock on LCSC</t>
   </si>
   <si>
-    <t>TTI Europe</t>
-  </si>
-  <si>
-    <t>Heisener</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
     <t>DC-C024E-7A-1.65</t>
   </si>
   <si>
+    <t>https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Murata-Electronics-GRM033R61E104KE14D_C76939.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_TDK-C1005X5R1E225KT000E_C76595.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Darfon-Elec-C0603X7R221KGT_C258475.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603KRX5R8BB475_C326580.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samsung-Electro-Mechanics-CL31B105KCHNNNE_C13832.html</t>
+  </si>
+  <si>
+    <t>https://www.ttieurope.com/content/ttieurope/en/apps/part-detail.html?partsNumber=VE-330M1ETR-0605&amp;mfgShortname=LEL&amp;utm=tti-octo&amp;channel=ppc&amp;source=octopart&amp;campaigns=tti-brand</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Bridge-Rectifiers_onsemi-DF06S_C105154.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_UNI-ROYAL-Uniroyal-Elec-0201WMF5102TEE_C473471.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_UNI-ROYAL-Uniroyal-Elec-0201WMF7153TEE_C620454.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_UNI-ROYAL-Uniroyal-Elec-NQ01WMJ0133TEE_C965341.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_LIZ-Elec-CR0603FA2200G_C100863.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/DC-DC-Converters_Texas-Instruments-LMR62014XMF-NOPB_C55182.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Optocouplers-Phototransistor-Output_onsemi-4N25SM_C258246.html</t>
+  </si>
+  <si>
+    <t>https://tr.aliexpress.com/item/32827253255.html?gatewayAdapt=glo2tur</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/USB-Connectors_TE-Connectivity-292303-1_C86461.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Inductors-SMD_TDK-SPM5012T-100M-LR_C2046913.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate </t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>C1608X5R1E475K080AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603KRX5R8BB475
+</t>
+  </si>
+  <si>
+    <t>---------</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stadium Board </t>
+  </si>
+  <si>
+    <t>B2020WS</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/span-style-background-color-ff0-Schottky-span-span-style-background-color-ff0-Barrier-span-span-style-background-color-ff0-Diodes-span-span-style-background-color-ff0-SBD-span_Changjiang-Electronics-Tech-CJ-B2020WS_C77284.html</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>RC1210FR-07560RL</t>
+  </si>
+  <si>
     <t>0805W8F1002T5E</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_YAGEO-RC1210FR-07560RL_C728387.html</t>
+  </si>
+  <si>
+    <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount_UNI-ROYAL-Uniroyal-Elec-0805W8F1002T5E_C17414.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -301,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -443,17 +503,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -464,28 +513,62 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -497,7 +580,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -522,9 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -549,9 +629,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,24 +647,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -606,18 +665,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -633,20 +683,59 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -923,523 +1012,505 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="42.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A1" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="A1" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="2" spans="1:6" ht="16.5" thickBot="1">
       <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60">
+      <c r="A3" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E3" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="29"/>
+    </row>
+    <row r="4" spans="1:6" ht="45">
+      <c r="A4" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="30"/>
+    </row>
+    <row r="5" spans="1:6" ht="45">
+      <c r="A5" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" spans="1:6" ht="45">
+      <c r="A6" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6" s="8" customFormat="1" ht="60">
+      <c r="A7" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="10">
+        <v>4</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" ht="90.75" thickBot="1">
+      <c r="A8" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="105.75" thickBot="1">
+      <c r="A9" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="17">
+        <v>2</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A10" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="17">
+        <v>2</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="32"/>
+    </row>
+    <row r="11" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="26">
+        <v>2</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="27"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A12" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26">
+        <v>2</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45">
+      <c r="A13" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="12">
+        <v>2</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="29"/>
+    </row>
+    <row r="14" spans="1:6" ht="45">
+      <c r="A14" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="33"/>
+    </row>
+    <row r="15" spans="1:6" ht="45">
+      <c r="A15" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:6" ht="45">
+      <c r="A16" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="45">
+      <c r="A17" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="7" customFormat="1" ht="45.75" thickBot="1">
+      <c r="A18" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="8" customFormat="1" ht="45">
+      <c r="A19" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="19">
+        <v>2</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="29"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="45">
+      <c r="A21" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A22" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="8" customFormat="1">
+      <c r="A23" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A3" s="36">
+      <c r="C23" s="20"/>
+      <c r="D23" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="13">
-        <v>3</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="40"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A4" s="36">
-        <v>2</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="41"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A5" s="36">
-        <v>3</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="42"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A6" s="36">
-        <v>4</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A7" s="36">
-        <v>5</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="11">
-        <v>4</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="41"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A8" s="36">
-        <v>6</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="16">
-        <v>1</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A9" s="36">
-        <v>7</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="19">
-        <v>2</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A10" s="36">
-        <v>8</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="19">
-        <v>2</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A11" s="36">
-        <v>9</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="34">
-        <v>2</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="35"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A12" s="36">
+      <c r="E23" s="13"/>
+      <c r="F23" s="48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="45">
+      <c r="A24" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="34">
-        <v>2</v>
-      </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A13" s="36">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="13">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="40"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A14" s="36">
-        <v>12</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="44"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A15" s="36">
-        <v>13</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="41"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A16" s="36">
-        <v>14</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A17" s="36">
-        <v>15</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A18" s="36">
-        <v>16</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="16">
-        <v>2</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="9" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="36">
-        <v>17</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="21">
-        <v>2</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="40"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A20" s="36">
-        <v>18</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A21" s="36">
-        <v>19</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="42"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A22" s="36">
-        <v>20</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="16">
-        <v>1</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="9" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A23" s="36">
-        <v>21</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="21">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A24" s="36">
-        <v>22</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>12</v>
-      </c>
       <c r="C24" s="6" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="41"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A25" s="36">
-        <v>23</v>
+      <c r="E24" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="49" t="s">
+        <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C25" s="6"/>
       <c r="D25" s="3">
         <v>1</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="39" t="s">
-        <v>57</v>
+      <c r="E25" s="9"/>
+      <c r="F25" s="33" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="26.25" thickBot="1">
-      <c r="A26" s="36">
-        <v>24</v>
-      </c>
-      <c r="B26" s="30" t="s">
+      <c r="A26" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="24">
+        <v>8</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="32">
-        <v>8</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>56</v>
+      <c r="F26" s="28" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
@@ -1471,27 +1542,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E8" r:id="rId16" xr:uid="{8537F03E-8899-43DA-B4A7-2B8A117DE469}"/>
-    <hyperlink ref="E9" r:id="rId17" xr:uid="{27AA9B92-09C1-4A5A-9BE5-16F692BB6C8C}"/>
-    <hyperlink ref="E22" r:id="rId18" xr:uid="{BF70A448-2700-48CC-9B35-ACBBDEFEA5A2}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>